--- a/Coupang_Top20_20260507.xlsx
+++ b/Coupang_Top20_20260507.xlsx
@@ -431,17 +431,17 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>productName</t>
+          <t>상품명</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>productPrice</t>
+          <t>가격</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>productUrl</t>
+          <t>링크</t>
         </is>
       </c>
     </row>
@@ -454,10 +454,9 @@
       <c r="B2" t="n">
         <v>23970</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=8300107736&amp;itemId=25246423475&amp;vendorItemId=90965273088&amp;traceid=V0-113-6d3bd893a0f3e865</t>
-        </is>
+      <c r="C2">
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=8300107736&amp;itemId=25246423475&amp;vendorItemId=90965273088&amp;traceid=V0-113-6d3bd893a0f3e865", "클릭해서 이동")</f>
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -469,280 +468,261 @@
       <c r="B3" t="n">
         <v>335790</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=9024163013&amp;itemId=26462308675&amp;vendorItemId=93437588392&amp;traceid=V0-113-848acafd9e852dbc</t>
-        </is>
+      <c r="C3">
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=9024163013&amp;itemId=26462308675&amp;vendorItemId=93437588392&amp;traceid=V0-113-848acafd9e852dbc", "클릭해서 이동")</f>
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>신지모루 아이폰 8핀 고속충전 라이트닝 케이블</t>
+          <t>아이리버 C타입-C타입 패브릭 초고속 충전 데이터 케이블 60W</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3900</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=7908137708&amp;itemId=21573867350&amp;vendorItemId=88625581419&amp;traceid=V0-113-379f5e8f329e61b4</t>
-        </is>
+        <v>4000</v>
+      </c>
+      <c r="C4">
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=8803472212&amp;itemId=25636725400&amp;vendorItemId=92626790654&amp;traceid=V0-113-4e0e1cdf04169745", "클릭해서 이동")</f>
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>로지텍 G102IC 2세대 LIGHTSYNC 게이밍 유선마우스</t>
+          <t>브리타 정수기 필터 막스트라 프로 퓨어 퍼포먼스 3입</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21180</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=6011227725&amp;itemId=28238141798&amp;vendorItemId=70778258892&amp;traceid=V0-113-38d0e1f44bf0cf88</t>
-        </is>
+        <v>21900</v>
+      </c>
+      <c r="C5">
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=9102889885&amp;itemId=23756832465&amp;vendorItemId=90781295338&amp;traceid=V0-113-59ae32451442015d", "클릭해서 이동")</f>
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>홈플래닛 핸디형 스탠드 스팀다리미</t>
+          <t>모디스 30W GaN PD 3.0 PPS 초고속 충전기 어댑터 + C to C 초고속 케이블 1.2m 세트</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>28990</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=310080038&amp;itemId=977484067&amp;vendorItemId=5392665218&amp;traceid=V0-113-c73a6d2a7fbf4b52</t>
-        </is>
+        <v>4900</v>
+      </c>
+      <c r="C6">
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=8810609759&amp;itemId=25665388705&amp;vendorItemId=92655005902&amp;traceid=V0-113-22b95ac8337c4b5b", "클릭해서 이동")</f>
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>요이치 USB 3.0 A타입 to C타입 플로우 C2 OTG 변환 젠더</t>
+          <t>신지모루 아이폰 8핀 고속충전 라이트닝 케이블</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1880</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=6978270723&amp;itemId=17038636697&amp;vendorItemId=84213534574&amp;traceid=V0-113-9e7d77440ccc4e5f</t>
-        </is>
+        <v>3900</v>
+      </c>
+      <c r="C7">
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=7908137708&amp;itemId=21573867350&amp;vendorItemId=88625581419&amp;traceid=V0-113-379f5e8f329e61b4", "클릭해서 이동")</f>
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>삼성전자 C타입 초고속 충전기 25W + 케이블 1m 세트 PD PPS GaN</t>
+          <t>신지모루 오피디 25W GaN 듀얼포트 PPS 초고속 PD 충전기</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24900</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=9058116499&amp;itemId=26591689978&amp;vendorItemId=94332189481&amp;traceid=V0-113-9c9b35eda2bf1e20</t>
-        </is>
+        <v>8980</v>
+      </c>
+      <c r="C8">
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=7415163807&amp;itemId=19222022188&amp;vendorItemId=86338760049&amp;traceid=V0-113-693c11efc2bbce39", "클릭해서 이동")</f>
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>신지모루 C to C PD 고속충전 케이블 60W</t>
+          <t>로지텍 G102IC 2세대 LIGHTSYNC 게이밍 유선마우스</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6900</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=8509349020&amp;itemId=13761827932&amp;vendorItemId=81012487257&amp;traceid=V0-113-fbdca8b1f131e189</t>
-        </is>
+        <v>21180</v>
+      </c>
+      <c r="C9">
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=6011227725&amp;itemId=28238141798&amp;vendorItemId=70778258892&amp;traceid=V0-113-38d0e1f44bf0cf88", "클릭해서 이동")</f>
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>유닉스 세라믹 판고데기</t>
+          <t>Apple 아이폰 17 자급제</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>24900</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=8729115745&amp;itemId=25361584612&amp;vendorItemId=3089081003&amp;traceid=V0-113-c054456fc302c5b1</t>
-        </is>
+        <v>1200990</v>
+      </c>
+      <c r="C10">
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=9024167492&amp;itemId=26462329849&amp;vendorItemId=93437609262&amp;traceid=V0-113-96f1bb4c89dba906", "클릭해서 이동")</f>
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>홈플래닛 퀄컴 공식인증 QC3.0 18W 고속충전기 + C타입 충전케이블 1.2m 세트</t>
+          <t>홈플래닛 핸디형 스탠드 스팀다리미</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7490</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=1628630781&amp;itemId=2778296479&amp;vendorItemId=89645323681&amp;traceid=V0-113-e16801aaf71b1d25</t>
-        </is>
+        <v>28990</v>
+      </c>
+      <c r="C11">
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=310080038&amp;itemId=977484067&amp;vendorItemId=5392665218&amp;traceid=V0-113-c73a6d2a7fbf4b52", "클릭해서 이동")</f>
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>필립스 무선 ENC노이즈캔슬링 블루투스 이어폰</t>
+          <t>요이치 USB 3.0 A타입 to C타입 플로우 C2 OTG 변환 젠더</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19900</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=8498887873&amp;itemId=24600675528&amp;vendorItemId=91612183770&amp;traceid=V0-113-53ee2dd24dc6f077</t>
-        </is>
+        <v>1880</v>
+      </c>
+      <c r="C12">
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=6978270723&amp;itemId=17038636697&amp;vendorItemId=84213534574&amp;traceid=V0-113-9e7d77440ccc4e5f", "클릭해서 이동")</f>
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>에버튼하우스 에그쿠커</t>
+          <t>PLEIGO USB 메모리 P50</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>9500</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=283693738&amp;itemId=18656743421&amp;vendorItemId=92385284024&amp;traceid=V0-113-c77feddeeb9a1c86</t>
-        </is>
+        <v>7500</v>
+      </c>
+      <c r="C13">
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=5309101612&amp;itemId=7654764554&amp;vendorItemId=74945175607&amp;traceid=V0-113-09bac7b5f3f4541f", "클릭해서 이동")</f>
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>아이리버 25W 2포트 초고속 가정용 충전기 + CtoC 케이블 세트</t>
+          <t>로지텍 무소음 무선 마우스</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8800</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=8939019740&amp;itemId=26138373322&amp;vendorItemId=93118512226&amp;traceid=V0-113-fd1e07a2d9481cd8</t>
-        </is>
+        <v>22900</v>
+      </c>
+      <c r="C14">
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=6159950381&amp;itemId=11948008563&amp;vendorItemId=3299873959&amp;traceid=V0-113-a5be5e5f7b0a2d69", "클릭해서 이동")</f>
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Apple 애플펜슬 프로</t>
+          <t>삼성전자 C타입 초고속 충전기 25W + 케이블 1m 세트 PD PPS GaN</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>182450</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=8106270209&amp;itemId=22947179438&amp;vendorItemId=89981484435&amp;traceid=V0-113-ba85b1c9289d1f3f</t>
-        </is>
+        <v>24900</v>
+      </c>
+      <c r="C15">
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=9058116499&amp;itemId=26591689978&amp;vendorItemId=94332189481&amp;traceid=V0-113-9c9b35eda2bf1e20", "클릭해서 이동")</f>
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>맥스틸 애플 아이폰 삼성 갤럭시 호환 C타입 오픈형 유선 이어폰, GM-EC20, 화이트</t>
+          <t>신지모루 C to C PD 고속충전 케이블 60W</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3920</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=8371538377&amp;itemId=24191384321&amp;vendorItemId=91477513891&amp;traceid=V0-113-3296e603157fd219</t>
-        </is>
+        <v>6900</v>
+      </c>
+      <c r="C16">
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=8509349020&amp;itemId=13761827932&amp;vendorItemId=81012487257&amp;traceid=V0-113-fbdca8b1f131e189", "클릭해서 이동")</f>
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>액센 프리미엄 캐릭터 마이크로 SD카드</t>
+          <t>홈플래닛 탁상용 접이식 스마트폰 거치대  6.5x11x12.5~16.5 cm</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>22800</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=7704604385&amp;itemId=6156844140&amp;vendorItemId=73453040955&amp;traceid=V0-113-a6ffe7d8068452b2</t>
-        </is>
+        <v>2980</v>
+      </c>
+      <c r="C17">
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=7265236509&amp;itemId=18515307151&amp;vendorItemId=85654104724&amp;traceid=V0-113-802cee97866e3ec9", "클릭해서 이동")</f>
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Apple 아이폰 17 Pro 자급제</t>
+          <t>유닉스 세라믹 판고데기</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1790000</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=9024167576&amp;itemId=26462330287&amp;vendorItemId=93437609640&amp;traceid=V0-113-81d4af092486a31f</t>
-        </is>
+        <v>24900</v>
+      </c>
+      <c r="C18">
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=8729115745&amp;itemId=25361584612&amp;vendorItemId=3089081003&amp;traceid=V0-113-c054456fc302c5b1", "클릭해서 이동")</f>
+        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Apple 2024 에어팟 4 블루투스 이어폰 유선충전</t>
+          <t>필립스 무선 ENC노이즈캔슬링 블루투스 이어폰</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>179340</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=8367073893&amp;itemId=24175708330&amp;vendorItemId=91193685697&amp;traceid=V0-113-b76fc3836f4c8921</t>
-        </is>
+        <v>19900</v>
+      </c>
+      <c r="C19">
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=8498887873&amp;itemId=24600675528&amp;vendorItemId=91612183770&amp;traceid=V0-113-53ee2dd24dc6f077", "클릭해서 이동")</f>
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>굿밸류 디스플레이 C타입-C타입 PD 100W 초고속 충전케이블</t>
+          <t>에버튼하우스 에그쿠커</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5900</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=8192535363&amp;itemId=23451383734&amp;vendorItemId=90478144994&amp;traceid=V0-113-fd4497c12f1e8e36</t>
-        </is>
+        <v>9500</v>
+      </c>
+      <c r="C20">
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=283693738&amp;itemId=18656743421&amp;vendorItemId=92385284024&amp;traceid=V0-113-c77feddeeb9a1c86", "클릭해서 이동")</f>
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>블라우풍트 전문가용 6step 풍속조절 초고출력 헤어드라이기 2400W</t>
+          <t>아이리버 25W 2포트 초고속 가정용 충전기 + CtoC 케이블 세트</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>22800</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=8584993909&amp;itemId=24887322820&amp;vendorItemId=91894001767&amp;traceid=V0-113-2494ed5ca6d6469b</t>
-        </is>
+        <v>8800</v>
+      </c>
+      <c r="C21">
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=8939019740&amp;itemId=26138373322&amp;vendorItemId=93118512226&amp;traceid=V0-113-fd1e07a2d9481cd8", "클릭해서 이동")</f>
+        <v/>
       </c>
     </row>
   </sheetData>
